--- a/hourly datasets/cap_gen_year20final.xlsx
+++ b/hourly datasets/cap_gen_year20final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1016322605355135</v>
+        <v>0.09875601761107693</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1331043532377512</v>
+        <v>0.133679861582728</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2347366137732647</v>
+        <v>0.2324358791938049</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1580679086825927</v>
+        <v>0.1592046389707417</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2597001692181062</v>
+        <v>0.2579606565818186</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04376156664135121</v>
+        <v>0.03887594611315912</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002529839505213326</v>
+        <v>0.001908077758361874</v>
       </c>
       <c r="D5" t="n">
-        <v>8.761641952528331</v>
+        <v>8.581125286747319</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01542800872070308</v>
+        <v>0.01018390432383887</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03879675392540394</v>
+        <v>0.03513126444787131</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04872637935729793</v>
+        <v>0.04262062777844749</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1453938271768647</v>
+        <v>0.137631963724236</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +559,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02783253679909668</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.001766389746154192</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.776274590672215</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.01275749563726479</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.02436808887859849</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.03129698471959536</v>
-      </c>
+        <v>0.02182674755993833</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1294647973346101</v>
+        <v>0.1205827651710153</v>
       </c>
     </row>
     <row r="7">
@@ -587,25 +577,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01834357672657711</v>
+        <v>0.01238656694215552</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001438133890871352</v>
+        <v>0.000778802733189487</v>
       </c>
       <c r="D7" t="n">
-        <v>3.184669944891964</v>
+        <v>2.668002362106391</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01534245702020938</v>
+        <v>0.01068795691499366</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01552136312821852</v>
+        <v>0.01085814254503709</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02116579032493603</v>
+        <v>0.01391499133927373</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1199758372620906</v>
+        <v>0.1111425845532324</v>
       </c>
     </row>
     <row r="8">
@@ -615,15 +605,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01162570027688834</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+        <v>0.005116309249733392</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0003720317223487465</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7164560301672895</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.001536042893397304</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.004386779909448343</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005845838590018435</v>
+      </c>
       <c r="H8" t="n">
-        <v>0.1132579608124018</v>
+        <v>0.1038723268608103</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +633,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01218648742028626</v>
+        <v>0.004234954184971049</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00105278393511706</v>
+        <v>0.0004482689106973763</v>
       </c>
       <c r="D9" t="n">
-        <v>1.383215647023965</v>
+        <v>0.7313349384736882</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006056334445960623</v>
+        <v>0.002523056187748473</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01012114568143264</v>
+        <v>0.003355573042952662</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01425182915913969</v>
+        <v>0.005114335326989302</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1138187479557997</v>
+        <v>0.102990971796048</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +661,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01164651242353386</v>
+        <v>0.004453834504737081</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001178678676683818</v>
+        <v>0.0003759470485336651</v>
       </c>
       <c r="D10" t="n">
-        <v>1.402255000863588</v>
+        <v>0.8160797594004051</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00763873425262017</v>
+        <v>0.00385062252302609</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009334718847606192</v>
+        <v>0.003716606676830689</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01395830599946176</v>
+        <v>0.005191062332643314</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1132787729590473</v>
+        <v>0.103209852115814</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03383545647285402</v>
+        <v>0.03362063737599964</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +697,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1354677170083675</v>
+        <v>0.1323766549870766</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05926678375606758</v>
+        <v>0.05762488638520889</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +715,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1608990442915811</v>
+        <v>0.1563809039962858</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07702324577357501</v>
+        <v>0.07542969214316485</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +733,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1786555063090885</v>
+        <v>0.1741857097542418</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08557982281271152</v>
+        <v>0.0835002742344859</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +751,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.187212083348225</v>
+        <v>0.1822562918455628</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09137061353124869</v>
+        <v>0.08845849581771674</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +769,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1930028740667621</v>
+        <v>0.1872145134287937</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09614514120463856</v>
+        <v>0.09438364177651021</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +787,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.197777401740152</v>
+        <v>0.1931396593875871</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0966519284594832</v>
+        <v>0.09526682497926202</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +805,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1982841889949967</v>
+        <v>0.1940228425903389</v>
       </c>
     </row>
     <row r="18">
@@ -815,22 +815,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1016322605355135</v>
+        <v>-0.09875601761107693</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008184724085594378</v>
+        <v>0.007670736813733694</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.78194440735432</v>
+        <v>-19.73456284842334</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0241487565814973</v>
+        <v>0.02320178087205987</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1177433714158163</v>
+        <v>-0.1138278606364006</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08552114965521068</v>
+        <v>-0.0836841745857536</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09991613980274094</v>
+        <v>0.09705040602770959</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +851,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.2015484003382544</v>
+        <v>0.1958064236387865</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1030089044794883</v>
+        <v>0.101266118460914</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -869,7 +869,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.2046411650150018</v>
+        <v>0.2000221360719909</v>
       </c>
     </row>
     <row r="21">
@@ -879,25 +879,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1069993869585494</v>
+        <v>0.1049490304324977</v>
       </c>
       <c r="C21" t="n">
-        <v>0.006737559737895482</v>
+        <v>0.006581352228098656</v>
       </c>
       <c r="D21" t="n">
-        <v>27.23521515254481</v>
+        <v>26.99413645867403</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04266115757544881</v>
+        <v>0.04287183554255741</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09374248010681115</v>
+        <v>0.09201753947586203</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1202562938102871</v>
+        <v>0.117880521389133</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2086316474940628</v>
+        <v>0.2037050480435746</v>
       </c>
     </row>
     <row r="22">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1112317171313762</v>
+        <v>0.1094072972473444</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -915,7 +915,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2128639776668896</v>
+        <v>0.2081633148584213</v>
       </c>
     </row>
     <row r="23">
@@ -925,25 +925,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.11472946700891</v>
+        <v>0.1134050489198647</v>
       </c>
       <c r="C23" t="n">
-        <v>0.006933558217167623</v>
+        <v>0.006754125391518487</v>
       </c>
       <c r="D23" t="n">
-        <v>28.76314926053296</v>
+        <v>28.79964750818885</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03970665460976443</v>
+        <v>0.04031943493704979</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1011106768971863</v>
+        <v>0.1001382914715215</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1283482571206334</v>
+        <v>0.1266718063682075</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2163617275444235</v>
+        <v>0.2121610665309416</v>
       </c>
     </row>
     <row r="24">
@@ -953,25 +953,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1191865821360233</v>
+        <v>0.1183237380386235</v>
       </c>
       <c r="C24" t="n">
-        <v>0.006561567039717055</v>
+        <v>0.006365155157501408</v>
       </c>
       <c r="D24" t="n">
-        <v>30.11727319675678</v>
+        <v>30.21951662071938</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03672389257228235</v>
+        <v>0.03684367526657614</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1062944953281114</v>
+        <v>0.1058175433508872</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1320786689439353</v>
+        <v>0.1308299327263593</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2208188426715368</v>
+        <v>0.2170797556497004</v>
       </c>
     </row>
     <row r="25">
@@ -981,25 +981,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1242988019061651</v>
+        <v>0.1231029607035039</v>
       </c>
       <c r="C25" t="n">
-        <v>0.006690923673680792</v>
+        <v>0.006541134576879031</v>
       </c>
       <c r="D25" t="n">
-        <v>30.792460216712</v>
+        <v>30.8418126307856</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03913274174929359</v>
+        <v>0.03707046882081846</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1111473941228753</v>
+        <v>0.11024613831883</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1374502096894548</v>
+        <v>0.135959783088178</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2259310624416785</v>
+        <v>0.2218589783145809</v>
       </c>
     </row>
     <row r="26">
@@ -1009,25 +1009,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.12590755635499</v>
+        <v>0.1247009813003714</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006783264532057268</v>
+        <v>0.006402194835136931</v>
       </c>
       <c r="D26" t="n">
-        <v>31.40931333238305</v>
+        <v>31.67775099234022</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03079473828585882</v>
+        <v>0.03005958177466682</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1125789749865675</v>
+        <v>0.1121235804513854</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1392361377234135</v>
+        <v>0.1372783821493578</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2275398168905035</v>
+        <v>0.2234569989114484</v>
       </c>
     </row>
     <row r="27">
@@ -1037,25 +1037,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1313646774139538</v>
+        <v>0.1311686146304859</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00646597891310742</v>
+        <v>0.006357891009179018</v>
       </c>
       <c r="D27" t="n">
-        <v>31.78002835819297</v>
+        <v>31.9947479838412</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03787074213135282</v>
+        <v>0.03535368725715106</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1186646448267631</v>
+        <v>0.1186814987537465</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1440647100011441</v>
+        <v>0.1436557305072259</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2329969379494672</v>
+        <v>0.2299246322415628</v>
       </c>
     </row>
     <row r="28">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1385421202412916</v>
+        <v>0.138768559765388</v>
       </c>
       <c r="C28" t="n">
-        <v>0.006929313523036389</v>
+        <v>0.006650142265526807</v>
       </c>
       <c r="D28" t="n">
-        <v>30.33036311964915</v>
+        <v>30.70932059570688</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06298901182335746</v>
+        <v>0.06124595138538357</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1249367251303649</v>
+        <v>0.1257112957870993</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1521475153522188</v>
+        <v>0.1518258237436773</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2401743807768051</v>
+        <v>0.2375245773764649</v>
       </c>
     </row>
     <row r="29">
@@ -1093,25 +1093,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0148064697366559</v>
+        <v>0.006463192663545776</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001128555487046371</v>
+        <v>0.0002924208523129828</v>
       </c>
       <c r="D29" t="n">
-        <v>2.379300267459233</v>
+        <v>1.566655675172048</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02966488404541591</v>
+        <v>0.03009008887845641</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01256775377464908</v>
+        <v>0.005889559722657315</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01704518569866261</v>
+        <v>0.007036825604434164</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1164387302721694</v>
+        <v>0.1052192102746227</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year20final.xlsx
+++ b/hourly datasets/cap_gen_year20final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2251373619891955</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09875601761107693</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1015070606457137</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.133679861582728</v>
+        <v>0.3971024976866627</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2324358791938049</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2734721963431809</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1592046389707417</v>
+        <v>0.3620628362184124</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2579606565818186</v>
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2384325348749306</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03887594611315912</v>
+        <v>0.4130634944125059</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001908077758361874</v>
+        <v>0.00449806653503904</v>
       </c>
       <c r="D5" t="n">
-        <v>8.581125286747319</v>
+        <v>11.82556049707391</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01018390432383887</v>
+        <v>0.01108462864668771</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03513126444787131</v>
+        <v>0.04357114205155377</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04262062777844749</v>
+        <v>0.06122055277668454</v>
       </c>
       <c r="H5" t="n">
-        <v>0.137631963724236</v>
+        <v>25</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2894331930690242</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +576,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02182674755993833</v>
+        <v>0.3907603211467047</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -567,7 +584,10 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1205827651710153</v>
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2671300198032229</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +597,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01238656694215552</v>
+        <v>0.3908233149537497</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000778802733189487</v>
+        <v>0.002311272729603504</v>
       </c>
       <c r="D7" t="n">
-        <v>2.668002362106391</v>
+        <v>12.44890832198443</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01068795691499366</v>
+        <v>0.0147838275685483</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01085814254503709</v>
+        <v>0.02859601203186906</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01391499133927373</v>
+        <v>0.03766291799804258</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1111425845532324</v>
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2671930136102679</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +628,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005116309249733392</v>
+        <v>0.3269446000307947</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003720317223487465</v>
+        <v>0.002459240326377722</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7164560301672895</v>
+        <v>-18.04620666404615</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001536042893397304</v>
+        <v>0.001669169780468595</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004386779909448343</v>
+        <v>-0.0413223431774776</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005845838590018435</v>
+        <v>-0.03167789897540129</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1038723268608103</v>
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2033142986873129</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +659,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004234954184971049</v>
+        <v>0.3231386918016105</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0004482689106973763</v>
+        <v>0.003075195523802567</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7313349384736882</v>
+        <v>-15.48729400838253</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002523056187748473</v>
+        <v>0.002791394867306093</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003355573042952662</v>
+        <v>-0.04723332607904828</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005114335326989302</v>
+        <v>-0.03517248589899192</v>
       </c>
       <c r="H9" t="n">
-        <v>0.102990971796048</v>
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1995083904581287</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +690,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004453834504737081</v>
+        <v>0.3262416176158422</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0003759470485336651</v>
+        <v>0.003088665021918142</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8160797594004051</v>
+        <v>-13.5026734786393</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00385062252302609</v>
+        <v>0.004325476550592144</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003716606676830689</v>
+        <v>-0.04281590498593003</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005191062332643314</v>
+        <v>-0.03070300201985818</v>
       </c>
       <c r="H10" t="n">
-        <v>0.103209852115814</v>
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2026113162723604</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +721,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03362063737599964</v>
+        <v>0.2779882773809569</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +729,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1323766549870766</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1543579760374751</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +742,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05762488638520889</v>
+        <v>0.3046194247135521</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +750,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1563809039962858</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1809891233700703</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +763,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07542969214316485</v>
+        <v>0.3245451049758607</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +771,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1741857097542418</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2009148036323789</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +784,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0835002742344859</v>
+        <v>0.3356870136257721</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +792,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1822562918455628</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2120567122822903</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +805,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08845849581771674</v>
+        <v>0.3425470620044144</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +813,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1872145134287937</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2189167606609326</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +826,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09438364177651021</v>
+        <v>0.3483398936910714</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +834,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1931396593875871</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2247095923475896</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +847,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09526682497926202</v>
+        <v>0.3526250788201641</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +855,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1940228425903389</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2289947774766823</v>
       </c>
     </row>
     <row r="18">
@@ -815,24 +868,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09875601761107693</v>
+        <v>0.1236303013434818</v>
       </c>
       <c r="C18" t="n">
-        <v>0.007670736813733694</v>
+        <v>0.008078359483076464</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.73456284842334</v>
+        <v>-20.91064520942806</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02320178087205987</v>
+        <v>0.0236433805598663</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1138278606364006</v>
+        <v>-0.1207256364475087</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0836841745857536</v>
+        <v>-0.08898345326216242</v>
       </c>
       <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -843,7 +899,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09705040602770959</v>
+        <v>0.3541058133254664</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +907,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1958064236387865</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2304755119819846</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +920,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.101266118460914</v>
+        <v>0.3566469296060666</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -869,7 +928,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.2000221360719909</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2330166282625848</v>
       </c>
     </row>
     <row r="21">
@@ -879,25 +941,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1049490304324977</v>
+        <v>0.3621256798133264</v>
       </c>
       <c r="C21" t="n">
-        <v>0.006581352228098656</v>
+        <v>0.006569698278870487</v>
       </c>
       <c r="D21" t="n">
-        <v>26.99413645867403</v>
+        <v>26.97116216072971</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04287183554255741</v>
+        <v>0.04285439332547671</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09201753947586203</v>
+        <v>0.09189267878535198</v>
       </c>
       <c r="G21" t="n">
-        <v>0.117880521389133</v>
+        <v>0.1177099075008554</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2037050480435746</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2384953784698446</v>
       </c>
     </row>
     <row r="22">
@@ -907,7 +972,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1094072972473444</v>
+        <v>0.3673090751084275</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -915,7 +980,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2081633148584213</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2436787737649457</v>
       </c>
     </row>
     <row r="23">
@@ -925,25 +993,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1134050489198647</v>
+        <v>0.3717093088557358</v>
       </c>
       <c r="C23" t="n">
-        <v>0.006754125391518487</v>
+        <v>0.00675022551953992</v>
       </c>
       <c r="D23" t="n">
-        <v>28.79964750818885</v>
+        <v>28.77880800777796</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04031943493704979</v>
+        <v>0.04029803403828957</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1001382914715215</v>
+        <v>0.1000588411794104</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1266718063682075</v>
+        <v>0.1265770464360628</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2121610665309416</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.248079007512254</v>
       </c>
     </row>
     <row r="24">
@@ -953,25 +1024,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1183237380386235</v>
+        <v>0.3783878264168508</v>
       </c>
       <c r="C24" t="n">
-        <v>0.006365155157501408</v>
+        <v>0.006360043760974183</v>
       </c>
       <c r="D24" t="n">
-        <v>30.21951662071938</v>
+        <v>30.19065455866591</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03684367526657614</v>
+        <v>0.03682054464783107</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1058175433508872</v>
+        <v>0.1057051203729291</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1308299327263593</v>
+        <v>0.1306974453945559</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2170797556497004</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.254757525073369</v>
       </c>
     </row>
     <row r="25">
@@ -981,25 +1055,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1231029607035039</v>
+        <v>0.3836913254091344</v>
       </c>
       <c r="C25" t="n">
-        <v>0.006541134576879031</v>
+        <v>0.006533151197680013</v>
       </c>
       <c r="D25" t="n">
-        <v>30.8418126307856</v>
+        <v>30.79886618381566</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03707046882081846</v>
+        <v>0.037040433965683</v>
       </c>
       <c r="F25" t="n">
-        <v>0.11024613831883</v>
+        <v>0.1100686213610248</v>
       </c>
       <c r="G25" t="n">
-        <v>0.135959783088178</v>
+        <v>0.1357509294214215</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2218589783145809</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2600610240656526</v>
       </c>
     </row>
     <row r="26">
@@ -1009,25 +1086,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1247009813003714</v>
+        <v>0.3892272513200497</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006402194835136931</v>
+        <v>0.006392490506270174</v>
       </c>
       <c r="D26" t="n">
-        <v>31.67775099234022</v>
+        <v>31.62023230641582</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03005958177466682</v>
+        <v>0.03003145222981276</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1121235804513854</v>
+        <v>0.1118837707215936</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1372783821493578</v>
+        <v>0.1370004888442708</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2234569989114484</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2655969499765679</v>
       </c>
     </row>
     <row r="27">
@@ -1037,25 +1117,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1311686146304859</v>
+        <v>0.3946325288159155</v>
       </c>
       <c r="C27" t="n">
-        <v>0.006357891009179018</v>
+        <v>0.006342101055715706</v>
       </c>
       <c r="D27" t="n">
-        <v>31.9947479838412</v>
+        <v>31.8921467484323</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03535368725715106</v>
+        <v>0.03531271621243778</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1186814987537465</v>
+        <v>0.1182509162989896</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1436557305072259</v>
+        <v>0.1431631975008813</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2299246322415628</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2710022274724337</v>
       </c>
     </row>
     <row r="28">
@@ -1065,25 +1148,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.138768559765388</v>
+        <v>0.4003418060891348</v>
       </c>
       <c r="C28" t="n">
-        <v>0.006650142265526807</v>
+        <v>0.006549243911599217</v>
       </c>
       <c r="D28" t="n">
-        <v>30.70932059570688</v>
+        <v>30.47388455739241</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06124595138538357</v>
+        <v>0.0610657619093254</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1257112957870993</v>
+        <v>0.1242480560019836</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1518258237436773</v>
+        <v>0.1499665380540324</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2375245773764649</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.276711504745653</v>
       </c>
     </row>
     <row r="29">
@@ -1093,25 +1179,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.006463192663545776</v>
+        <v>0.3703446359471164</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0002924208523129828</v>
+        <v>0.001548147902268131</v>
       </c>
       <c r="D29" t="n">
-        <v>1.566655675172048</v>
+        <v>2.043339133985594</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03009008887845641</v>
+        <v>0.7635703632228116</v>
       </c>
       <c r="F29" t="n">
-        <v>0.005889559722657315</v>
+        <v>0.004900964737417042</v>
       </c>
       <c r="G29" t="n">
-        <v>0.007036825604434164</v>
+        <v>0.01097284469471781</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1052192102746227</v>
+        <v>55</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2467143346036346</v>
       </c>
     </row>
   </sheetData>
